--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0037.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0037.xlsx
@@ -8051,7 +8051,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Thông thạo bốn ngôn ngữ, am hiểu tám kỹ năng, nhưng ta chỉ muốn giữ vững một công việc thôi...</t>
+          <t>Thông thạo bốn ngôn ngữ, am hiểu tám kỹ năng, nhưng tao chỉ muốn giữ vững một công việc thôi...</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Cậu chạy được mấy vòng rồi? Lại đây nghỉ ngơi với tớ đi.</t>
+          <t>Mày chạy được mấy vòng rồi? Lại đây nghỉ ngơi với tớ đi.</t>
         </is>
       </c>
     </row>
@@ -26521,7 +26521,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Ta sẽ không mắc bẫy đó lần thứ hai đâu!</t>
+          <t>Tao sẽ không mắc bẫy đó lần thứ hai đâu!</t>
         </is>
       </c>
     </row>
@@ -26911,7 +26911,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Nhưng khi chúng nhìn lên Ma Trận Sao, chúng sẽ nhớ đến những gì ta đã làm, phải không?</t>
+          <t>Nhưng khi chúng nhìn lên Ma Trận Sao, chúng sẽ nhớ đến những gì tao đã làm, phải không?</t>
         </is>
       </c>
     </row>
